--- a/templates/retention-reconciliation.xlsx
+++ b/templates/retention-reconciliation.xlsx
@@ -54,13 +54,13 @@
     </x:font>
     <x:font>
       <x:sz val="10"/>
-      <x:color rgb="FFFFFFFF"/>
+      <x:color rgb="FFFFFFF0"/>
       <x:name val="Arial"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="10"/>
-      <x:color rgb="FFFFFFFF"/>
+      <x:color rgb="FFFFFFF0"/>
       <x:name val="Arial"/>
     </x:font>
     <x:font>
@@ -78,7 +78,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF243747"/>
+        <x:fgColor rgb="FF000000"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -86,7 +86,7 @@
     <x:border/>
     <x:border>
       <x:top style="thin">
-        <x:color rgb="FF71808C"/>
+        <x:color rgb="FF6E6862"/>
       </x:top>
     </x:border>
   </x:borders>
@@ -192,21 +192,21 @@
     <x:dxf>
       <x:font>
         <x:b/>
-        <x:color rgb="FF9B2925"/>
+        <x:color rgb="FF990024"/>
       </x:font>
       <x:fill>
         <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFDE9E7"/>
+          <x:bgColor rgb="FFF0D9DE"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:font>
-        <x:color rgb="FF7B4B00"/>
+        <x:color rgb="FF990024"/>
       </x:font>
       <x:fill>
         <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFFF0D4"/>
+          <x:bgColor rgb="FFF0D9DE"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -225,34 +225,34 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="FFFFF0"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="66023C"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="990024"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="E5E4E2"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="6E6862"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="B1AFAD"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="DCDAD7"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="66023C"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="990024"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
